--- a/output/pdf_financials_xlsx/JJJ.xlsx
+++ b/output/pdf_financials_xlsx/JJJ.xlsx
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.024</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.139845</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.321057</v>
       </c>
     </row>
     <row r="93">
@@ -3682,7 +3682,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/JJJ.xlsx
+++ b/output/pdf_financials_xlsx/JJJ.xlsx
@@ -648,7 +648,7 @@
         <v>0</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.0006579999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -963,7 +963,7 @@
         <v>-0.208993</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.208993</v>
+        <v>-0.208335</v>
       </c>
     </row>
     <row r="28">
@@ -1001,7 +1001,7 @@
         <v>-0.208993</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.208993</v>
+        <v>-0.208335</v>
       </c>
     </row>
     <row r="30">
@@ -1096,13 +1096,13 @@
         </is>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.018304</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.059922</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.68094</v>
       </c>
     </row>
     <row r="35">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.018304</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.059922</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.68094</v>
       </c>
     </row>
     <row r="37">
@@ -1390,13 +1390,13 @@
         </is>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.018304</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.059922</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.68094</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">

--- a/output/pdf_financials_xlsx/JJJ.xlsx
+++ b/output/pdf_financials_xlsx/JJJ.xlsx
@@ -1789,19 +1789,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.061362</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.035172</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.035172</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.033705</v>
       </c>
     </row>
     <row r="68">
